--- a/source/sold_listings.xlsx
+++ b/source/sold_listings.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24260" windowHeight="12420"/>
+    <workbookView windowWidth="27780" windowHeight="16640"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>MLS Number</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Sale/Lease Price</t>
   </si>
   <si>
-    <t>362 Lafayette Ave #A, Cliffside Park, NJ 07010</t>
+    <t>475 Oakdene Ave #1, Cliffside Park, NJ 07010</t>
   </si>
   <si>
     <t>Buyer</t>
@@ -68,148 +68,13 @@
     <t>Not provided</t>
   </si>
   <si>
-    <t>12/09/2025</t>
-  </si>
-  <si>
-    <t>12/22/2025</t>
-  </si>
-  <si>
-    <t>1060 Anderson Ave, Fort Lee, NJ 07024</t>
-  </si>
-  <si>
-    <t>08/01/2025</t>
-  </si>
-  <si>
-    <t>10/7/2025</t>
-  </si>
-  <si>
-    <t>441 Elizabeth St, Fort Lee, NJ 07024</t>
-  </si>
-  <si>
-    <t>06/18/2025</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
-  </si>
-  <si>
-    <t>12 Thistle Ct, Totowa, NJ 07512</t>
-  </si>
-  <si>
-    <t>07/08/2025</t>
-  </si>
-  <si>
-    <t>09/29/2025</t>
-  </si>
-  <si>
-    <t>76 Franklin St, Verona, NJ 07044</t>
-  </si>
-  <si>
-    <t>06/27/2025</t>
-  </si>
-  <si>
-    <t>08/19/2025</t>
-  </si>
-  <si>
-    <t>211 70th St #3, Guttenberg, NJ 07093</t>
-  </si>
-  <si>
-    <t>Seller</t>
-  </si>
-  <si>
-    <t>05/06/2025</t>
-  </si>
-  <si>
-    <t>08/08/2025</t>
-  </si>
-  <si>
-    <t>73 White Beeches Dr, Dumont, NJ 07628</t>
-  </si>
-  <si>
-    <t>06/04/2025</t>
-  </si>
-  <si>
-    <t>08/05/2025</t>
-  </si>
-  <si>
-    <t>2350 Linwood Ave #4D, Fort Lee, NJ 07024</t>
-  </si>
-  <si>
-    <t>05/22/2025</t>
-  </si>
-  <si>
-    <t>07/07/2025</t>
-  </si>
-  <si>
-    <t>502 Longview Pl, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
-    <t>03/22/2025</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>9 Heatherhill Rd, Demarest, NJ 07627</t>
-  </si>
-  <si>
-    <t>10/23/2024</t>
-  </si>
-  <si>
-    <t>05/16/2025</t>
-  </si>
-  <si>
-    <t>781 Jefferson Ave #781, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
-    <t>3300+/-</t>
-  </si>
-  <si>
-    <t>12/13/2024</t>
-  </si>
-  <si>
-    <t>05/05/2025</t>
-  </si>
-  <si>
-    <t>220 Washington Pl, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
-    <t>03/18/2025</t>
-  </si>
-  <si>
-    <t>04/25/2025</t>
-  </si>
-  <si>
-    <t>771 Jefferson Ave #771, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
-    <t>04/02/2025</t>
-  </si>
-  <si>
-    <t>475 Oakdene Ave #1, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
     <t>09/17/2024</t>
   </si>
   <si>
     <t>02/21/2025</t>
   </si>
   <si>
-    <t>7020 Polk St #8, Guttenberg, NJ 07093</t>
-  </si>
-  <si>
-    <t>11/05/2024</t>
-  </si>
-  <si>
-    <t>02/04/2025</t>
-  </si>
-  <si>
-    <t>504 Stockton Ct #504, Edgewater, NJ 07020</t>
-  </si>
-  <si>
-    <t>09/25/2024</t>
-  </si>
-  <si>
-    <t>12/19/2024</t>
+    <t>475 Oakdene Ave #2, Cliffside Park, NJ 07010</t>
   </si>
   <si>
     <t>65 Columbia Ave, Cliffside Park, NJ 07010</t>
@@ -219,42 +84,6 @@
   </si>
   <si>
     <t>09/12/2024</t>
-  </si>
-  <si>
-    <t>211 70th St #2, Guttenberg, NJ 07093</t>
-  </si>
-  <si>
-    <t>05/22/2024</t>
-  </si>
-  <si>
-    <t>08/19/2024</t>
-  </si>
-  <si>
-    <t>224 The Promenade #224, Edgewater, NJ 07020</t>
-  </si>
-  <si>
-    <t>05/03/2024</t>
-  </si>
-  <si>
-    <t>07/31/2024</t>
-  </si>
-  <si>
-    <t>660 Bloomfield Ave #206, Bloomfield, NJ 07003</t>
-  </si>
-  <si>
-    <t>11/08/2023</t>
-  </si>
-  <si>
-    <t>05/17/2024</t>
-  </si>
-  <si>
-    <t>750 River Rd, Teaneck, NJ 07666</t>
-  </si>
-  <si>
-    <t>02/15/2024</t>
-  </si>
-  <si>
-    <t>05/01/2024</t>
   </si>
 </sst>
 </file>
@@ -443,7 +272,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,6 +287,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -643,7 +478,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -662,17 +497,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -801,7 +625,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -813,119 +637,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -934,67 +758,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="26" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="26" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="26" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-      <extLst>
-        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
-          <etc:displayText val="2"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1521,8 +1299,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col min="2" max="2" width="13.6153846153846" customWidth="1"/>
     <col min="3" max="3" width="56.7307692307692" customWidth="1"/>
@@ -1566,739 +1344,109 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="17.55" spans="1:11">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4">
-        <v>25042812</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="4">
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
+        <v>24030115</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>4</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="5">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="5">
+        <v>122</v>
+      </c>
+      <c r="K2" s="7">
+        <v>1099000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="4">
+        <v>15</v>
+      </c>
+      <c r="B3" s="5">
+        <v>24030115</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4">
-        <v>2</v>
-      </c>
-      <c r="K2" s="6">
-        <v>1199000</v>
-      </c>
-    </row>
-    <row r="3" ht="17.55" spans="1:11">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4">
-        <v>25027445</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4">
-        <v>4</v>
-      </c>
-      <c r="F3" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="4">
-        <v>46</v>
-      </c>
-      <c r="K3" s="6">
-        <v>1680000</v>
+      <c r="J3" s="5">
+        <v>122</v>
+      </c>
+      <c r="K3" s="7">
+        <v>1099000</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7">
-        <v>25021347</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="4">
         <v>18</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="B4" s="5">
+        <v>24025637</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>3</v>
       </c>
-      <c r="F4" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="7">
-        <v>44</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1588000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1">
-        <v>5</v>
-      </c>
-      <c r="B5" s="7">
-        <v>25023732</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7">
-        <v>4</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="7">
-        <v>31</v>
-      </c>
-      <c r="K5" s="9">
-        <v>1260000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1">
-        <v>6</v>
-      </c>
-      <c r="B6" s="7">
-        <v>25022536</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7">
-        <v>4</v>
-      </c>
-      <c r="F6" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="7">
-        <v>21</v>
-      </c>
-      <c r="K6" s="9">
-        <v>899000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="1">
+      <c r="H4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="5">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
-        <v>25015168</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="7">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1500</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7">
-        <v>42</v>
-      </c>
-      <c r="K7" s="9">
-        <v>695000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="1">
-        <v>8</v>
-      </c>
-      <c r="B8" s="7">
-        <v>25018957</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4</v>
-      </c>
-      <c r="F8" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="7">
-        <v>13</v>
-      </c>
-      <c r="K8" s="9">
-        <v>699000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="1">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7">
-        <v>25017229</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>855</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="7">
-        <v>13</v>
-      </c>
-      <c r="K9" s="9">
-        <v>369000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="1">
-        <v>10</v>
-      </c>
-      <c r="B10" s="7">
-        <v>25009198</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3</v>
-      </c>
-      <c r="F10" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="7">
-        <v>13</v>
-      </c>
-      <c r="K10" s="9">
-        <v>949000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="1">
-        <v>11</v>
-      </c>
-      <c r="B11" s="7">
-        <v>24034194</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7">
-        <v>6</v>
-      </c>
-      <c r="F11" s="7">
-        <v>6.5</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="7">
-        <v>103</v>
-      </c>
-      <c r="K11" s="9">
-        <v>2790000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="1">
-        <v>12</v>
-      </c>
-      <c r="B12" s="7">
-        <v>24038929</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3</v>
-      </c>
-      <c r="F12" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="7">
-        <v>111</v>
-      </c>
-      <c r="K12" s="9">
-        <v>1399000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="1">
-        <v>13</v>
-      </c>
-      <c r="B13" s="7">
-        <v>25008555</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>4</v>
-      </c>
-      <c r="F13" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="G13" s="7">
-        <v>3350</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="7">
-        <v>13</v>
-      </c>
-      <c r="K13" s="9">
-        <v>1389000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="1">
-        <v>14</v>
-      </c>
-      <c r="B14" s="7">
-        <v>24038930</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3</v>
-      </c>
-      <c r="F14" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="7">
-        <v>55</v>
-      </c>
-      <c r="K14" s="9">
-        <v>1399000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="1">
-        <v>15</v>
-      </c>
-      <c r="B15" s="7">
-        <v>24030115</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="7">
-        <v>4</v>
-      </c>
-      <c r="F15" s="7">
-        <v>3</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="7">
-        <v>122</v>
-      </c>
-      <c r="K15" s="9">
-        <v>1099000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="1">
-        <v>16</v>
-      </c>
-      <c r="B16" s="7">
-        <v>24035588</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <v>544</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J16" s="7">
-        <v>20</v>
-      </c>
-      <c r="K16" s="9">
-        <v>209000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="1">
-        <v>17</v>
-      </c>
-      <c r="B17" s="7">
-        <v>24031048</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3</v>
-      </c>
-      <c r="F17" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="7">
-        <v>61</v>
-      </c>
-      <c r="K17" s="9">
-        <v>655000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="1">
-        <v>18</v>
-      </c>
-      <c r="B18" s="7">
-        <v>24025637</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3</v>
-      </c>
-      <c r="F18" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J18" s="7">
-        <v>7</v>
-      </c>
-      <c r="K18" s="9">
+      <c r="K4" s="7">
         <v>975000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="1">
-        <v>19</v>
-      </c>
-      <c r="B19" s="7">
-        <v>24015947</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3</v>
-      </c>
-      <c r="F19" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="G19" s="7">
-        <v>1550</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="7">
-        <v>54</v>
-      </c>
-      <c r="K19" s="9">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="1">
-        <v>20</v>
-      </c>
-      <c r="B20" s="7">
-        <v>24013510</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>850</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="7">
-        <v>37</v>
-      </c>
-      <c r="K20" s="9">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="1">
-        <v>21</v>
-      </c>
-      <c r="B21" s="7">
-        <v>23034377</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2</v>
-      </c>
-      <c r="F21" s="7">
-        <v>2</v>
-      </c>
-      <c r="G21" s="7">
-        <v>1070</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" s="7">
-        <v>154</v>
-      </c>
-      <c r="K21" s="9">
-        <v>595000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" s="7">
-        <v>24004671</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3</v>
-      </c>
-      <c r="F22" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J22" s="7">
-        <v>13</v>
-      </c>
-      <c r="K22" s="9">
-        <v>630000</v>
       </c>
     </row>
   </sheetData>

--- a/source/sold_listings.xlsx
+++ b/source/sold_listings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27780" windowHeight="16640"/>
+    <workbookView windowWidth="27780" windowHeight="16040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
   <si>
     <t>MLS Number</t>
   </si>
@@ -35,55 +35,1427 @@
     <t>Property Address</t>
   </si>
   <si>
-    <t>Represents</t>
-  </si>
-  <si>
     <t>Beds</t>
   </si>
   <si>
     <t>Baths</t>
   </si>
   <si>
-    <t>Sq Ft</t>
-  </si>
-  <si>
-    <t>Listing Date</t>
-  </si>
-  <si>
     <t>Sale Date</t>
   </si>
   <si>
-    <t>Days on Market</t>
-  </si>
-  <si>
     <t>Sale/Lease Price</t>
   </si>
   <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>362 Lafayette Ave #A, Cliffside Park, NJ 07010</t>
+  </si>
+  <si>
+    <t>12/22/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- New construction townhouse with four levels of luxury living</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 4 bedrooms, 3 full baths, 2 half baths including a primary suite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Modern kitchen with quartz countertops and contemporary finishes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Finished ground level with separate entrance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Top-floor entertainment space with wet bar and private rooftop patio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private driveway, garage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime location near parks, shopping, schools, and transportation</t>
+    </r>
+  </si>
+  <si>
+    <t>441 Elizabeth St, Fort Lee, NJ 07024</t>
+  </si>
+  <si>
+    <t>10/1/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Oversized four-level contemporary new-construction townhome in prime Fort Lee location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 3 bedrooms, 4.5 bathrooms including a spa-inspired primary suite with heated floors and soaking tub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Chef’s kitchen with European cabinetry, integrated appliances, wine cooler, and oversized island</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Open living areas with expansive Andersen windows and wide-plank European flooring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Ground level with office, recreation room, full bath, and direct backyard access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private outdoor spaces including deck off kitchen, rooftop deck, and fenced backyard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Smart home features, multi-zone HVAC, central vacuum, security cameras, and attached garage — minutes to the GW Bridge</t>
+    </r>
+  </si>
+  <si>
+    <t>12 Thistle Ct, Totowa, NJ 07512</t>
+  </si>
+  <si>
+    <t>9/29/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Brand-new luxury Colonial with 5 bedrooms and 4 full bathrooms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Grand two-story foyer, high ceilings, and open-concept floor plan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Custom kitchen with quartz countertops, stainless steel appliances, and premium finishes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Primary suite with walk-in closets and spa-style bathroom, plus a junior suite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- First-floor guest bedroom for added flexibility and convenience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Fully finished basement ideal for recreation, gym, office, or entertainment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Cul-de-sac location with private backyard and attached two-car garage</t>
+    </r>
+  </si>
+  <si>
+    <t>9 Heatherhill Rd, Demarest, NJ 07627</t>
+  </si>
+  <si>
+    <t>5/16/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Nearly new luxury Colonial designed by award-winning architect Robert Zampolin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 6 bedrooms and 6.5 bathrooms, including multiple en-suite bedrooms and a grand primary suite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Open-concept main level with 10-foot ceilings, two-story foyer, and great room</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Designer kitchen with high-end WOLF and SUB-ZERO appliances</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Fully finished basement with theater, gym, wet bar, bedroom, and steam shower bath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private backyard oasis with patio and hot tub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Quiet street location with top-rated schools and convenient NYC access</t>
+    </r>
+  </si>
+  <si>
+    <t>781 Jefferson Ave #781, Cliffside Park, NJ 07010</t>
+  </si>
+  <si>
+    <t>5/5/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Oversized luxury townhouse (approx. 3,300+ SF) with three levels of living space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 3 bedrooms, 3.5 bathrooms including a primary suite with dual walk-in closets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Chef’s kitchen with outdoor deck, wine closet, and wet bar with beverage refrigerator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Spacious main level with living room, dining room, family room, and gas fireplace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Ground level with recreation room or office, full bath, mudroom, and yard access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Extra-deep two-car garage plus wide foyer and abundant storage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime north Cliffside Park location bordering Fort Lee, close to parks, shopping, and transportation</t>
+    </r>
+  </si>
+  <si>
+    <t>220 Washington Pl, Cliffside Park, NJ 07010</t>
+  </si>
+  <si>
+    <t>4/25/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Four-level contemporary new-construction townhome with approx. 3,350 SF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 4 bedrooms and 4.5 bathrooms including a spa-style primary suite with heated floors and soaking tub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private rooftop terrace with unobstructed Manhattan skyline views</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Gourmet chef’s kitchen with European cabinetry, integrated appliances, wine cooler, and large island</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Ground level with bedroom, full bath, recreation room, wet bar, and fenced backyard access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Top-floor bonus space with full bath and wet bar — ideal for office, lounge, or guest suite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Central Cliffside Park location close to parks, shopping, transportation, and NYC commute</t>
+    </r>
+  </si>
+  <si>
+    <t>771 Jefferson Ave #771, Cliffside Park, NJ 07010</t>
+  </si>
+  <si>
+    <t>4/2/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Oversized luxury townhouse (approx. 3,300+ SF) with three levels of living space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 3 bedrooms, 3.5 bathrooms including a primary suite with dual walk-in closets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Chef’s kitchen with outdoor deck, wine closet, wet bar, and beverage refrigerator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Spacious main level with living room, dining room, family room, and gas fireplace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Ground level with recreation room or office, full bath, mudroom, and yard access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Extra-wide two-car garage plus generous foyer and storage space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime north Cliffside Park location bordering Fort Lee, close to parks, shopping, and transportation</t>
+    </r>
+  </si>
+  <si>
     <t>475 Oakdene Ave #1, Cliffside Park, NJ 07010</t>
   </si>
   <si>
-    <t>Buyer</t>
-  </si>
-  <si>
-    <t>Not provided</t>
-  </si>
-  <si>
-    <t>09/17/2024</t>
-  </si>
-  <si>
-    <t>02/21/2025</t>
+    <t>2/21/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Brand-new duplex condo on a quiet residential street</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 4 bedrooms and 3 full bathrooms including a primary suite with walk-in closet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Modern kitchen with two-toned cabinetry, quartz countertops, and GE Café appliances</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Spacious living area with integrated fireplace and open dining space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Finished ground level with recreation room, additional bedroom/office, and full bath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private enclosed yard with sliding glass door access plus deck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Attached garage with additional parking and convenient Cliffside Park location</t>
+    </r>
   </si>
   <si>
     <t>475 Oakdene Ave #2, Cliffside Park, NJ 07010</t>
   </si>
   <si>
-    <t>65 Columbia Ave, Cliffside Park, NJ 07010</t>
-  </si>
-  <si>
-    <t>08/08/2024</t>
-  </si>
-  <si>
-    <t>09/12/2024</t>
+    <t>4/30/2025</t>
+  </si>
+  <si>
+    <t>Off market presale</t>
+  </si>
+  <si>
+    <t>669 Summit St, Englewood Cliff, NJ 07632</t>
+  </si>
+  <si>
+    <t>6 baths 2 half baths</t>
+  </si>
+  <si>
+    <t>11/13/2025</t>
+  </si>
+  <si>
+    <t>439 Elizabeth St, Fort Lee, NJ 07024</t>
+  </si>
+  <si>
+    <t>7/10/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- New construction townhouse with 3 bedrooms and 4.5 bathrooms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Finished basement plus in-unit laundry for added convenience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Modern systems including central air, tankless hot water, and multi-source heating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Two gas fireplaces for added comfort and ambiance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Private outdoor spaces including terrace and deck/patio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Attached garage with additional parking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Prime Fort Lee location close to parks, schools, shopping, and transportation</t>
+    </r>
+  </si>
+  <si>
+    <t>1531 11th st, Fort Lee, NJ 07024</t>
+  </si>
+  <si>
+    <t>7/9/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Spacious home featuring 6 bedrooms and 3 full bathrooms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Central air and multi-zone heating and cooling for year-round comfort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- In-unit laundry for convenience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Unfinished basement offering potential for customization or expansion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Hardwood floors throughout (as is)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- 1-car garage with tandem parking plus additional parking space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
+      <t>- Located in Fort Lee with sunrise and sunset views, close to local amenities</t>
+    </r>
+  </si>
+  <si>
+    <t>off market presale</t>
+  </si>
+  <si>
+    <t>1060 Anderson Ave, Fort Lee, NJ 07024</t>
+  </si>
+  <si>
+    <t>10/7/2025</t>
+  </si>
+  <si>
+    <r>
+      <t>- Oversized contemporary new-construction townhome with tall ceilings throughout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 4 bedrooms, 4.5 bathrooms including a spa-style primary suite with heated floors and soaking tub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Chef’s kitchen with European cabinetry, oversized island, integrated appliances, and wine cooler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Open-concept main level with wide-plank wood flooring and floor-to-ceiling windows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Fully finished ground level with home office, wet bar, recreation area, and full bath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Smart home technology, multi-zone HVAC, central vacuum, and security camera system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Private outdoor deck, fenced backyard, two-car garage, plus additional parking — minutes to GW Bridge</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -106,23 +1478,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF444746"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Roboto"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -272,7 +1642,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,13 +1651,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF356854"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFF6F8F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,7 +1854,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -487,17 +1863,182 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color rgb="FF356854"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF356854"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,7 +2166,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -637,142 +2178,208 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1299,154 +2906,331 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="13.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="56.7307692307692" customWidth="1"/>
-    <col min="8" max="8" width="15.0576923076923" customWidth="1"/>
-    <col min="10" max="10" width="15.7019230769231" customWidth="1"/>
-    <col min="11" max="11" width="26.9230769230769" customWidth="1"/>
+    <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
+    <col min="2" max="2" width="56.7307692307692" customWidth="1"/>
+    <col min="6" max="6" width="17.2980769230769" customWidth="1"/>
+    <col min="7" max="7" width="15.0576923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1">
+    <row r="1" ht="31.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:7">
+      <c r="A2" s="4">
+        <v>25042812</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>4</v>
+      </c>
+      <c r="D2" s="7">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="20">
+        <v>1170000</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:7">
+      <c r="A3" s="8">
+        <v>25021347</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="D3" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="22">
+        <v>1550000</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:7">
+      <c r="A4" s="4">
+        <v>25023732</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="20">
+        <v>1260000</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="409.5" spans="1:7">
+      <c r="A5" s="8">
+        <v>24034194</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10">
+        <v>6</v>
+      </c>
+      <c r="D5" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="22">
+        <v>2650000</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:7">
+      <c r="A6" s="4">
+        <v>24038929</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="20">
+        <v>1300000</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="409.5" spans="1:7">
+      <c r="A7" s="8">
+        <v>25008555</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="10">
+        <v>4</v>
+      </c>
+      <c r="D7" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="22">
+        <v>1320000</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="409.5" spans="1:7">
+      <c r="A8" s="4">
+        <v>24038930</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="20">
+        <v>1295000</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="409.5" spans="1:7">
+      <c r="A9" s="8">
+        <v>24030115</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="10">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11">
+        <v>3</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="22">
+        <v>999000</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="17.55" spans="1:7">
+      <c r="A10" s="4">
+        <v>24035115</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="20">
+        <v>949000</v>
+      </c>
+      <c r="G10" s="24"/>
+    </row>
+    <row r="11" ht="31.75" spans="1:7">
+      <c r="A11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="10">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="D11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="22">
+        <v>4300000</v>
+      </c>
+      <c r="G11" s="25"/>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="4">
-        <v>15</v>
-      </c>
-      <c r="B2" s="5">
-        <v>24030115</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="5">
+    <row r="12" ht="409.5" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="20">
+        <v>1500000</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" ht="409.5" spans="1:7">
+      <c r="A13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="14">
         <v>4</v>
       </c>
-      <c r="F2" s="5">
-        <v>3</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5">
-        <v>122</v>
-      </c>
-      <c r="K2" s="7">
-        <v>1099000</v>
+      <c r="D13" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="26">
+        <v>1700000</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="4">
-        <v>15</v>
-      </c>
-      <c r="B3" s="5">
-        <v>24030115</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5">
+    <row r="14" ht="409.5" spans="1:7">
+      <c r="A14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="18">
         <v>4</v>
       </c>
-      <c r="F3" s="5">
-        <v>3</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="5">
-        <v>122</v>
-      </c>
-      <c r="K3" s="7">
-        <v>1099000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="4">
-        <v>18</v>
-      </c>
-      <c r="B4" s="5">
-        <v>24025637</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="5">
-        <v>7</v>
-      </c>
-      <c r="K4" s="7">
-        <v>975000</v>
+      <c r="D14" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="28">
+        <v>1600000</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/source/sold_listings.xlsx
+++ b/source/sold_listings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27780" windowHeight="16040"/>
+    <workbookView windowWidth="26100" windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>MLS Number</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Features</t>
   </si>
   <si>
+    <t>imgid</t>
+  </si>
+  <si>
     <t>362 Lafayette Ave #A, Cliffside Park, NJ 07010</t>
   </si>
   <si>
@@ -57,6 +60,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- New construction townhouse with four levels of luxury living</t>
     </r>
     <r>
@@ -182,6 +191,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Oversized four-level contemporary new-construction townhome in prime Fort Lee location</t>
     </r>
     <r>
@@ -307,6 +322,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Brand-new luxury Colonial with 5 bedrooms and 4 full bathrooms</t>
     </r>
     <r>
@@ -432,6 +453,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Nearly new luxury Colonial designed by award-winning architect Robert Zampolin</t>
     </r>
     <r>
@@ -557,6 +584,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Oversized luxury townhouse (approx. 3,300+ SF) with three levels of living space</t>
     </r>
     <r>
@@ -682,6 +715,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Four-level contemporary new-construction townhome with approx. 3,350 SF</t>
     </r>
     <r>
@@ -807,6 +846,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Oversized luxury townhouse (approx. 3,300+ SF) with three levels of living space</t>
     </r>
     <r>
@@ -932,6 +977,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Brand-new duplex condo on a quiet residential street</t>
     </r>
     <r>
@@ -1068,6 +1119,9 @@
     <t>11/13/2025</t>
   </si>
   <si>
+    <t>669 Summit st</t>
+  </si>
+  <si>
     <t>439 Elizabeth St, Fort Lee, NJ 07024</t>
   </si>
   <si>
@@ -1075,6 +1129,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- New construction townhouse with 3 bedrooms and 4.5 bathrooms</t>
     </r>
     <r>
@@ -1200,6 +1260,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <rFont val="Roboto"/>
+        <charset val="134"/>
+      </rPr>
       <t>- Spacious home featuring 6 bedrooms and 3 full bathrooms</t>
     </r>
     <r>
@@ -1328,6 +1394,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>- Oversized contemporary new-construction townhome with tall ceilings throughout</t>
     </r>
     <r>
@@ -1455,6 +1528,450 @@
         <scheme val="minor"/>
       </rPr>
       <t>- Private outdoor deck, fenced backyard, two-car garage, plus additional parking — minutes to GW Bridge</t>
+    </r>
+  </si>
+  <si>
+    <t>1060 Anderson</t>
+  </si>
+  <si>
+    <t>252 South St Unit 48G, New York, NY 10002</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Spacious 2-bedroom, 2-bath condo (~1,156 SF) with open layout and gourmet kitchen with breakfast bar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Private outdoor space plus in-unit washer/dryer for added convenience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Located in a luxury high-rise building with 20-year tax abatement (421a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Full-service amenities including doorman, concierge, valet, parking, and storage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Resort-style features: pool, gym, hot tub, media room, and children’s playroom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Extensive shared outdoor spaces including deck, garden, and patio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Prime Two Bridges location with access to transit, dining, and waterfront living</t>
+    </r>
+  </si>
+  <si>
+    <t>252 South Street</t>
+  </si>
+  <si>
+    <t>300 West 30th Street, New York, NY 10001</t>
+  </si>
+  <si>
+    <t>6/12/2025</t>
+  </si>
+  <si>
+    <t>300 West 30th Street</t>
+  </si>
+  <si>
+    <t>281 Central Avenue #PH5A, Jersey City, NJ 07307</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Exclusive penthouse with approx. 1,828 SF, 3 bedrooms, and 2.5 bathrooms</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Private elevator entry opening to a spacious foyer and expansive layout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Stunning Manhattan skyline views from every room</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Private rooftop deck ideal for entertaining and outdoor living</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Modern design with integrated smart home technology</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- In-unit washer/dryer, dishwasher, and central air for everyday convenience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Located in Jersey City Heights with easy access to transit and nearby neighborhoods</t>
+    </r>
+  </si>
+  <si>
+    <t>281 Central Avenue</t>
+  </si>
+  <si>
+    <t>2187 Jones Road, Fort Lee, NJ 07024</t>
+  </si>
+  <si>
+    <t>05/16/2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- New construction townhouse with 3 bedrooms, 4 full baths, and 2 half baths</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Four-level layout including rooftop with recreation space, skylights, and terrace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Open main level with kitchen, living, dining, family room, and walk-out terrace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Two en-suite bedrooms plus a spacious primary suite with dedicated bath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Ground level with recreation room, office, full bath, and backyard access</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Two-car attached garage with additional storage and central vacuum system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Prime Fort Lee location close to parks, schools, shopping, and NYC transportation</t>
     </r>
   </si>
 </sst>
@@ -1462,7 +1979,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="24" formatCode="\$#,##0_);[Red]\(\$#,##0\)"/>
     <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2290,7 +2808,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2348,6 +2866,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2380,6 +2901,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="24" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2906,8 +3433,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
     <col min="2" max="2" width="56.7307692307692" customWidth="1"/>
@@ -2915,7 +3442,7 @@
     <col min="7" max="7" width="15.0576923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.75" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2934,8 +3461,11 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:7">
@@ -2943,7 +3473,7 @@
         <v>25042812</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6">
         <v>4</v>
@@ -2952,13 +3482,13 @@
         <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="20">
+        <v>9</v>
+      </c>
+      <c r="F2" s="21">
         <v>1170000</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>9</v>
+      <c r="G2" s="22" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:7">
@@ -2966,7 +3496,7 @@
         <v>25021347</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="10">
         <v>3</v>
@@ -2975,13 +3505,13 @@
         <v>4.5</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="22">
+        <v>12</v>
+      </c>
+      <c r="F3" s="23">
         <v>1550000</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>12</v>
+      <c r="G3" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:7">
@@ -2989,7 +3519,7 @@
         <v>25023732</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="6">
         <v>5</v>
@@ -2998,13 +3528,13 @@
         <v>4</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="20">
+        <v>15</v>
+      </c>
+      <c r="F4" s="21">
         <v>1260000</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>15</v>
+      <c r="G4" s="22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="409.5" spans="1:7">
@@ -3012,7 +3542,7 @@
         <v>24034194</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10">
         <v>6</v>
@@ -3021,13 +3551,13 @@
         <v>6.5</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="22">
+        <v>18</v>
+      </c>
+      <c r="F5" s="23">
         <v>2650000</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>18</v>
+      <c r="G5" s="24" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:7">
@@ -3035,7 +3565,7 @@
         <v>24038929</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6">
         <v>3</v>
@@ -3044,13 +3574,13 @@
         <v>3.5</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="20">
+        <v>21</v>
+      </c>
+      <c r="F6" s="21">
         <v>1300000</v>
       </c>
-      <c r="G6" s="21" t="s">
-        <v>21</v>
+      <c r="G6" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:7">
@@ -3058,7 +3588,7 @@
         <v>25008555</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10">
         <v>4</v>
@@ -3067,13 +3597,13 @@
         <v>4.5</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="22">
+        <v>24</v>
+      </c>
+      <c r="F7" s="23">
         <v>1320000</v>
       </c>
-      <c r="G7" s="23" t="s">
-        <v>24</v>
+      <c r="G7" s="24" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="409.5" spans="1:7">
@@ -3081,7 +3611,7 @@
         <v>24038930</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="6">
         <v>3</v>
@@ -3090,13 +3620,13 @@
         <v>3.5</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="20">
+        <v>27</v>
+      </c>
+      <c r="F8" s="21">
         <v>1295000</v>
       </c>
-      <c r="G8" s="21" t="s">
-        <v>27</v>
+      <c r="G8" s="22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:7">
@@ -3104,7 +3634,7 @@
         <v>24030115</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="10">
         <v>4</v>
@@ -3113,13 +3643,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="22">
+        <v>30</v>
+      </c>
+      <c r="F9" s="23">
         <v>999000</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>30</v>
+      <c r="G9" s="24" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="17.55" spans="1:7">
@@ -3127,7 +3657,7 @@
         <v>24035115</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="6">
         <v>3</v>
@@ -3136,40 +3666,43 @@
         <v>2.5</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="20">
+        <v>33</v>
+      </c>
+      <c r="F10" s="21">
         <v>949000</v>
       </c>
-      <c r="G10" s="24"/>
+      <c r="G10" s="25"/>
     </row>
-    <row r="11" ht="31.75" spans="1:7">
+    <row r="11" ht="31.75" spans="1:8">
       <c r="A11" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="10">
         <v>5</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="22">
+        <v>37</v>
+      </c>
+      <c r="F11" s="23">
         <v>4300000</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="26"/>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" ht="409.5" spans="1:7">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="6">
         <v>3</v>
@@ -3178,21 +3711,21 @@
         <v>4.5</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="20">
+        <v>40</v>
+      </c>
+      <c r="F12" s="21">
         <v>1500000</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>39</v>
+      <c r="G12" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="409.5" spans="1:7">
       <c r="A13" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="14">
         <v>4</v>
@@ -3201,21 +3734,21 @@
         <v>4.5</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="26">
+        <v>43</v>
+      </c>
+      <c r="F13" s="27">
         <v>1700000</v>
       </c>
-      <c r="G13" s="27" t="s">
-        <v>42</v>
+      <c r="G13" s="28" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="14" ht="409.5" spans="1:7">
+    <row r="14" ht="409.5" spans="1:8">
       <c r="A14" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" s="18">
         <v>4</v>
@@ -3224,13 +3757,109 @@
         <v>4.5</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="28">
+        <v>47</v>
+      </c>
+      <c r="F14" s="29">
         <v>1600000</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>46</v>
+      <c r="G14" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" ht="409.5" spans="1:8">
+      <c r="A15" s="16">
+        <v>7586048</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="18">
+        <v>4</v>
+      </c>
+      <c r="D15" s="16">
+        <v>2</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="29">
+        <v>2325610</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" ht="409.5" spans="1:8">
+      <c r="A16" s="19"/>
+      <c r="B16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="18">
+        <v>2</v>
+      </c>
+      <c r="D16" s="16">
+        <v>2</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="32">
+        <v>1075000</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" ht="409.5" spans="1:8">
+      <c r="A17" s="16">
+        <v>240020251</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="18">
+        <v>3</v>
+      </c>
+      <c r="D17" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" ht="409.5" spans="1:7">
+      <c r="A18" s="16">
+        <v>25007204</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="18">
+        <v>3</v>
+      </c>
+      <c r="D18" s="16">
+        <v>5</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="32">
+        <v>1450000</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/source/sold_listings.xlsx
+++ b/source/sold_listings.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
   <si>
     <t>MLS Number</t>
   </si>
@@ -1119,6 +1119,16 @@
     <t>11/13/2025</t>
   </si>
   <si>
+    <t>"- 22’ ceiling great room with fireplace
+- Chef’s kitchen + full prep kitchen
+- Private primary suite with balcony &amp; fireplace
+- Mini golf court and pool
+- Fully finished entertainment level (media room, gym, billiards)
+- Smart home wiring + EV-ready
+-  Multi-zone radiant heat
+- 3-car heated garage + whole-house generator"</t>
+  </si>
+  <si>
     <t>669 Summit st</t>
   </si>
   <si>
@@ -1259,129 +1269,7 @@
     <t>7/9/2025</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- Spacious home featuring 6 bedrooms and 3 full bathrooms</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- Central air and multi-zone heating and cooling for year-round comfort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- In-unit laundry for convenience</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- Unfinished basement offering potential for customization or expansion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- Hardwood floors throughout (as is)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- 1-car garage with tandem parking plus additional parking space</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF434343"/>
-        <rFont val="Roboto"/>
-        <charset val="134"/>
-      </rPr>
-      <t>- Located in Fort Lee with sunrise and sunset views, close to local amenities</t>
-    </r>
+    <t>-Oversized contemporary new construction townhome.                                                                                    -a PRIVATE ELEVATOR &amp; PRIVATE HOME THEATER.                                                                                           -2 private decks, and fenced backyard. Floor to Ceiling Andersen windows and European wide plank flooring ---The chef's kitchen boasts European cabinetry, integrated fridge/freezer, wine cooler, and oversized island.                                                                                                              -Smart home features, multi-zone HVAC, central vacuum, security cameras, and oversized modern all-glass garage door with WiFi</t>
   </si>
   <si>
     <t>off market presale</t>
@@ -1682,6 +1570,15 @@
   </si>
   <si>
     <t>6/12/2025</t>
+  </si>
+  <si>
+    <t>- Prime Midtown location just one block from Penn Station, near Hudson Yards, Chelsea Market, and Times Square
+- New construction (2023) 1-bedroom residence with east-facing floor-to-ceiling windows
+- Modern island kitchen with integrated Miele appliances and white marble countertops
+- Spa-inspired bathroom with radiant heated floors, rain shower, and premium finishes
+- Private balcony with city views plus in-unit washer and dryer
+- Luxury amenities including 24-hour concierge, fitness center, media room, and outdoor space
+- Excellent transit access (Subway, NJ Transit, Amtrak, LIRR) and on-site grocery retail</t>
   </si>
   <si>
     <t>300 West 30th Street</t>
@@ -2866,47 +2763,53 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="24" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3439,10 +3342,11 @@
     <col min="1" max="1" width="13.6153846153846" customWidth="1"/>
     <col min="2" max="2" width="56.7307692307692" customWidth="1"/>
     <col min="6" max="6" width="17.2980769230769" customWidth="1"/>
-    <col min="7" max="7" width="15.0576923076923" customWidth="1"/>
+    <col min="7" max="7" width="41.8173076923077" customWidth="1"/>
+    <col min="8" max="8" width="9.69230769230769"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="17.55" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3461,7 +3365,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -3484,10 +3388,10 @@
       <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="20">
         <v>1170000</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3507,10 +3411,10 @@
       <c r="E3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="22">
         <v>1550000</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="23" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3530,10 +3434,10 @@
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>1260000</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3553,10 +3457,10 @@
       <c r="E5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="22">
         <v>2650000</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3576,10 +3480,10 @@
       <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>1300000</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3599,10 +3503,10 @@
       <c r="E7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>1320000</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="23" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3622,10 +3526,10 @@
       <c r="E8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>1295000</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="21" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3645,14 +3549,14 @@
       <c r="E9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="22">
         <v>999000</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="17.55" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10" s="4">
         <v>24035115</v>
       </c>
@@ -3668,12 +3572,12 @@
       <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <v>949000</v>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="24"/>
     </row>
-    <row r="11" ht="31.75" spans="1:8">
+    <row r="11" ht="350.75" spans="1:8">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
@@ -3689,20 +3593,22 @@
       <c r="E11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="22">
         <v>4300000</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="25" t="s">
+        <v>38</v>
+      </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="12" ht="409.5" spans="1:7">
+    <row r="12" ht="409.5" spans="1:8">
       <c r="A12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="6">
         <v>3</v>
@@ -3711,21 +3617,24 @@
         <v>4.5</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="21">
+        <v>41</v>
+      </c>
+      <c r="F12" s="20">
         <v>1500000</v>
       </c>
-      <c r="G12" s="22" t="s">
-        <v>41</v>
+      <c r="G12" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12">
+        <v>25021347</v>
       </c>
     </row>
-    <row r="13" ht="409.5" spans="1:7">
+    <row r="13" ht="183.75" spans="1:7">
       <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="14">
         <v>4</v>
@@ -3734,21 +3643,21 @@
         <v>4.5</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="27">
+        <v>44</v>
+      </c>
+      <c r="F13" s="26">
         <v>1700000</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>44</v>
+      <c r="G13" s="33" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="14" ht="409.5" spans="1:8">
+    <row r="14" ht="228.75" spans="1:8">
       <c r="A14" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="18">
         <v>4</v>
@@ -3757,24 +3666,24 @@
         <v>4.5</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="29">
+        <v>48</v>
+      </c>
+      <c r="F14" s="28">
         <v>1600000</v>
       </c>
-      <c r="G14" s="30" t="s">
-        <v>48</v>
+      <c r="G14" s="29" t="s">
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="15" ht="409.5" spans="1:8">
-      <c r="A15" s="16">
-        <v>7586048</v>
+    <row r="15" ht="228.75" spans="1:8">
+      <c r="A15" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="18">
         <v>4</v>
@@ -3782,47 +3691,49 @@
       <c r="D15" s="16">
         <v>2</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="29">
+      <c r="E15" s="30"/>
+      <c r="F15" s="28">
         <v>2325610</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="16" ht="409.5" spans="1:8">
-      <c r="A16" s="19"/>
+    <row r="16" ht="228.75" spans="1:8">
+      <c r="A16" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="B16" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" s="32">
         <v>1075000</v>
       </c>
-      <c r="G16" s="31" t="s">
-        <v>51</v>
+      <c r="G16" s="34" t="s">
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="17" ht="409.5" spans="1:8">
+    <row r="17" ht="213.75" spans="1:8">
       <c r="A17" s="16">
         <v>240020251</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="18">
         <v>3</v>
@@ -3830,13 +3741,13 @@
       <c r="D17" s="16">
         <v>2.5</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:7">
@@ -3844,7 +3755,7 @@
         <v>25007204</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" s="18">
         <v>3</v>
@@ -3853,13 +3764,13 @@
         <v>5</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F18" s="32">
         <v>1450000</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
